--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPI_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPI_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPI_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPI_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="BJ4" s="6" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="BJ5" s="6" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="AT6" s="6" t="n">
-        <v>46655</v>
+        <v>46656</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="BJ6" s="6" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="BJ7" s="6" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="BJ8" s="6" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="BJ9" s="6" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="BJ10" s="6" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="BJ11" s="6" t="n">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="BJ12" s="6" t="n">
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="BJ13" s="6" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45898</v>
+        <v>45899</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="BJ14" s="6" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="BJ15" s="6" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="BJ16" s="6" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="BJ17" s="6" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="BJ18" s="6" t="n">
-        <v>45955</v>
+        <v>45956</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="BJ19" s="6" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="BJ20" s="6" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="BJ21" s="6" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45778</v>
+        <v>45779</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="BJ22" s="6" t="n">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="BJ23" s="6" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="S24" s="6" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="T24" s="5" t="n">
         <v>3</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="BJ24" s="6" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="BJ25" s="6" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="BJ26" s="6" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         </is>
       </c>
       <c r="BJ27" s="6" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="BJ28" s="6" t="n">
-        <v>45773</v>
+        <v>45774</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="BJ29" s="6" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="BJ30" s="6" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="BJ31" s="6" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="BJ32" s="6" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="S33" s="6" t="n">
-        <v>46673</v>
+        <v>46674</v>
       </c>
       <c r="T33" s="5" t="n">
         <v>18</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="BJ33" s="6" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
